--- a/assets/files/hdfc-financial-model.xlsx
+++ b/assets/files/hdfc-financial-model.xlsx
@@ -15,7 +15,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peer Comps" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Cover'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Assumptions'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Historical'!$A$1:$J$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Forecast'!$A$1:$H$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Valuation'!$A$1:$H$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Ratios'!$A$1:$J$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Peer Comps'!$A$1:$G$35</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
 </file>
@@ -456,7 +464,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="251">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -1143,6 +1151,9 @@
     <xf numFmtId="3" fontId="30" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="170" fontId="30" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="170" fontId="24" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1395,7 +1406,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -1464,7 +1475,6 @@
       <c r="E6" s="171" t="n"/>
       <c r="F6" s="171" t="n"/>
     </row>
-    <row r="7"/>
     <row r="8" ht="15" customHeight="1" s="68">
       <c r="B8" s="172" t="inlineStr">
         <is>
@@ -1472,7 +1482,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="15" customHeight="1" s="68">
       <c r="A10" s="173" t="inlineStr">
         <is>
@@ -1562,8 +1571,6 @@
         <v/>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20" ht="15" customHeight="1" s="68">
       <c r="A20" s="173" t="inlineStr">
         <is>
@@ -1618,8 +1625,6 @@
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29" ht="15" customHeight="1" s="68">
       <c r="B29" s="172" t="inlineStr">
         <is>
@@ -1629,8 +1634,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -1639,7 +1644,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -1719,11 +1724,11 @@
     <row r="5" ht="15" customHeight="1" s="68">
       <c r="A5" s="189" t="inlineStr">
         <is>
-          <t>Current share price (₹, 24-Jun-2026)</t>
+          <t>Current share price (₹, 18-Jul-2026)</t>
         </is>
       </c>
       <c r="B5" s="190" t="n">
-        <v>784.9</v>
+        <v>785</v>
       </c>
       <c r="C5" s="90" t="n"/>
       <c r="D5" s="90" t="n"/>
@@ -2040,8 +2045,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -2050,7 +2055,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -3139,8 +3144,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -3149,7 +3154,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -3684,8 +3689,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -3694,7 +3699,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -4309,8 +4314,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4319,7 +4324,7 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
@@ -4868,8 +4873,8 @@
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
 
@@ -4878,9 +4883,9 @@
   <sheetPr filterMode="0">
     <tabColor rgb="FF004C8F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="42" customWidth="1" style="67" min="1" max="1"/>
@@ -4971,16 +4976,16 @@
         </is>
       </c>
       <c r="B5" s="190" t="n">
-        <v>784.9</v>
+        <v>785</v>
       </c>
       <c r="C5" s="190" t="n">
-        <v>49.39</v>
+        <v>49.5</v>
       </c>
       <c r="D5" s="190" t="n">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="E5" s="206" t="n">
-        <v>79219</v>
+        <v>74670</v>
       </c>
       <c r="F5" s="237">
         <f>IF(C5&gt;0,B5/C5,"n/a")</f>
@@ -4998,7 +5003,7 @@
         </is>
       </c>
       <c r="B6" s="190" t="n">
-        <v>1280</v>
+        <v>1460</v>
       </c>
       <c r="C6" s="190" t="n">
         <v>75.70999999999999</v>
@@ -5093,8 +5098,6 @@
         <v/>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="238" t="inlineStr">
         <is>
@@ -5141,11 +5144,10 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="238" t="inlineStr">
         <is>
-          <t>VALUATION TRIANGULATION — FOOTBALL FIELD</t>
+          <t>VALUATION TRIANGULATION — FOOTBALL FIELD (multi-method)</t>
         </is>
       </c>
       <c r="B17" s="165" t="n"/>
@@ -5180,7 +5182,7 @@
     <row r="19">
       <c r="A19" s="244" t="inlineStr">
         <is>
-          <t>Excess-return / RI</t>
+          <t>Excess-return / Residual Income (intrinsic)</t>
         </is>
       </c>
       <c r="B19" s="242">
@@ -5199,61 +5201,177 @@
     <row r="20">
       <c r="A20" s="244" t="inlineStr">
         <is>
-          <t>Comparable companies</t>
+          <t>Justified P/B — normalized ROE (intrinsic)</t>
         </is>
       </c>
       <c r="B20" s="242">
-        <f>B15*0.9</f>
+        <f>B32*0.9</f>
         <v/>
       </c>
       <c r="C20" s="242">
-        <f>B15</f>
+        <f>B32</f>
         <v/>
       </c>
       <c r="D20" s="242">
-        <f>B15*1.1</f>
+        <f>B32*1.1</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="239" t="inlineStr">
         <is>
-          <t>Blended target (70% intrinsic / 30% comps)</t>
-        </is>
+          <t>Comparable companies — P/B</t>
+        </is>
+      </c>
+      <c r="B21" s="248">
+        <f>B15*0.9</f>
+        <v/>
       </c>
       <c r="C21" s="245">
-        <f>0.7*Valuation!B19+0.3*B15</f>
+        <f>B15</f>
+        <v/>
+      </c>
+      <c r="D21" s="248">
+        <f>B15*1.1</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="244" t="inlineStr">
         <is>
-          <t>Current market price (₹)</t>
-        </is>
+          <t>Comparable companies — P/E</t>
+        </is>
+      </c>
+      <c r="B22" s="248">
+        <f>B35*0.9</f>
+        <v/>
       </c>
       <c r="C22" s="242">
-        <f>B5</f>
+        <f>B35</f>
+        <v/>
+      </c>
+      <c r="D22" s="248">
+        <f>B35*1.1</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="239" t="inlineStr">
         <is>
-          <t>Implied upside / (downside)</t>
-        </is>
-      </c>
-      <c r="C23" s="246">
-        <f>C21/B5-1</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24"/>
+          <t>Blended target (70% intrinsic / 30% comps)</t>
+        </is>
+      </c>
+      <c r="C23" s="245">
+        <f>0.7*AVERAGE(Valuation!B19,B32)+0.3*AVERAGE(B15,B35)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="67" t="inlineStr">
+        <is>
+          <t>Current market price (₹)</t>
+        </is>
+      </c>
+      <c r="C24" s="67">
+        <f>B5</f>
+        <v/>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" s="247" t="inlineStr">
         <is>
-          <t>Peer multiples researched as of Jun 2026 (Kotak price to be verified). Refresh peer inputs before publication.</t>
-        </is>
+          <t>Implied upside / (downside)</t>
+        </is>
+      </c>
+      <c r="C25" s="249">
+        <f>C23/B5-1</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>DDM (Gordon): light cross-check only — ~30% payout; RI captures retained value. Reported ROE ~14% depressed by HDFC Ltd merger, normalizing toward 16%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="238" t="inlineStr">
+        <is>
+          <t>INTRINSIC MULTIPLE — JUSTIFIED P/B (Gordon, normalized ROE)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="239" t="inlineStr">
+        <is>
+          <t>Sustainable ROE (normalized; reported ~14% recovering)</t>
+        </is>
+      </c>
+      <c r="B28" s="250" t="n">
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="239" t="inlineStr">
+        <is>
+          <t>Sustainable growth g</t>
+        </is>
+      </c>
+      <c r="B29" s="250">
+        <f>Assumptions!B23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="239" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B30" s="250">
+        <f>Assumptions!B22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="239" t="inlineStr">
+        <is>
+          <t>Justified P/B = (ROE − g)/(Ke − g)</t>
+        </is>
+      </c>
+      <c r="B31" s="241">
+        <f>(B28-B29)/(B30-B29)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="239" t="inlineStr">
+        <is>
+          <t>Justified-P/B implied value = P/B × BVPS (₹)</t>
+        </is>
+      </c>
+      <c r="B32" s="242">
+        <f>B31*D5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="238" t="inlineStr">
+        <is>
+          <t>MARKET MULTIPLE — P/E-IMPLIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="239" t="inlineStr">
+        <is>
+          <t>P/E-implied value = peer median P/E × EPS (₹)</t>
+        </is>
+      </c>
+      <c r="B35" s="242">
+        <f>B13*C5</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -5262,7 +5380,7 @@
     <mergeCell ref="A17:G17"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup orientation="landscape" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>